--- a/downloads/10.5281_zenodo.19682386/parc_alignedstudies.xlsx
+++ b/downloads/10.5281_zenodo.19682386/parc_alignedstudies.xlsx
@@ -1076,23 +1076,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="28.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="31.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="136.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="17.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="71.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="25.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="11.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="45.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="19.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="8.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -1808,23 +1791,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="32.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="78.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="17.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="52.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="25.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="11.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="45.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="19.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="8.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -2540,23 +2506,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="29.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="17.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="136.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="17.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="89.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="25.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="11.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="45.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="19.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="8.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
